--- a/nursing/フォーマット/06_事故苦情ヒヤリ様式/05_職員名簿・資格証台帳.xlsx
+++ b/nursing/フォーマット/06_事故苦情ヒヤリ様式/05_職員名簿・資格証台帳.xlsx
@@ -26,31 +26,32 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
+      <name val="Meiryo"/>
       <b val="1"/>
-      <color rgb="000E7490"/>
-      <sz val="13"/>
+      <color rgb="00163A2B"/>
+      <sz val="16"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
+      <name val="Meiryo"/>
+      <color rgb="005C665C"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <i val="1"/>
-      <color rgb="006B7280"/>
-      <sz val="9"/>
+      <name val="Meiryo"/>
+      <color rgb="00283129"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
+      <name val="Meiryo"/>
+      <i val="1"/>
+      <color rgb="005C665C"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="Meiryo UI"/>
-      <color rgb="006B7280"/>
-      <sz val="8"/>
     </font>
   </fonts>
   <fills count="4">
@@ -62,16 +63,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000E7490"/>
+        <fgColor rgb="00A9854A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8FAFC"/>
+        <fgColor rgb="00F6EDDA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -80,32 +81,69 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <bottom style="medium">
+        <color rgb="00A9854A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A9854A"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A9854A"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A9854A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A9854A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00DAD3C2"/>
+      </left>
+      <right style="thin">
+        <color rgb="00DAD3C2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DAD3C2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DAD3C2"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00A9854A"/>
+      </left>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -469,387 +507,351 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>職員名簿・資格証台帳</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>実地指導で確認される人員配置・資格要件の根拠資料。資格証の写しを別途保管</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>職種</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>雇用形態</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>入社日</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>資格・免許名</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>免許証番号</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>取得年月日</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>有効期限</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>更新研修
-期限</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>保有資格</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>資格登録番号</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>常勤換算</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>入職日</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>退職日</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>研修受講状況</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>山田 花子</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>（例）山田花子</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>看護師</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>常勤</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>2022/4/1</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>看護師免許</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>第123456号</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>2015/3/20</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>管理者兼務</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="4" t="inlineStr"/>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="4" t="inlineStr"/>
-      <c r="B5" s="4" t="inlineStr"/>
-      <c r="C5" s="4" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>正看護師</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>第○○号</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>2024/04/01</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>virtual等修了</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="4" t="inlineStr"/>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>（例）佐藤太郎</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>サビ管</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>常勤</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>サービス管理責任者</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>2023/10/01</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>基礎/実践研修修了</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="4" t="inlineStr"/>
-      <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="4" t="inlineStr"/>
-      <c r="J7" s="4" t="inlineStr"/>
+      <c r="A7" s="6" t="n"/>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="4" t="inlineStr"/>
-      <c r="B8" s="4" t="inlineStr"/>
-      <c r="C8" s="4" t="inlineStr"/>
-      <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="4" t="inlineStr"/>
-      <c r="J8" s="4" t="inlineStr"/>
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="4" t="inlineStr"/>
-      <c r="B9" s="4" t="inlineStr"/>
-      <c r="C9" s="4" t="inlineStr"/>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr"/>
-      <c r="I9" s="4" t="inlineStr"/>
-      <c r="J9" s="4" t="inlineStr"/>
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="4" t="inlineStr"/>
-      <c r="B10" s="4" t="inlineStr"/>
-      <c r="C10" s="4" t="inlineStr"/>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr"/>
-      <c r="I10" s="4" t="inlineStr"/>
-      <c r="J10" s="4" t="inlineStr"/>
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="6" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="4" t="inlineStr"/>
-      <c r="B11" s="4" t="inlineStr"/>
-      <c r="C11" s="4" t="inlineStr"/>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr"/>
-      <c r="I11" s="4" t="inlineStr"/>
-      <c r="J11" s="4" t="inlineStr"/>
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="6" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="4" t="inlineStr"/>
-      <c r="B12" s="4" t="inlineStr"/>
-      <c r="C12" s="4" t="inlineStr"/>
-      <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr"/>
-      <c r="I12" s="4" t="inlineStr"/>
-      <c r="J12" s="4" t="inlineStr"/>
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n"/>
+      <c r="J12" s="6" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="4" t="inlineStr"/>
-      <c r="B13" s="4" t="inlineStr"/>
-      <c r="C13" s="4" t="inlineStr"/>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="4" t="inlineStr"/>
-      <c r="I13" s="4" t="inlineStr"/>
-      <c r="J13" s="4" t="inlineStr"/>
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n"/>
+      <c r="J13" s="6" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="4" t="inlineStr"/>
-      <c r="B14" s="4" t="inlineStr"/>
-      <c r="C14" s="4" t="inlineStr"/>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr"/>
-      <c r="I14" s="4" t="inlineStr"/>
-      <c r="J14" s="4" t="inlineStr"/>
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="6" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="4" t="inlineStr"/>
-      <c r="B15" s="4" t="inlineStr"/>
-      <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr"/>
-      <c r="I15" s="4" t="inlineStr"/>
-      <c r="J15" s="4" t="inlineStr"/>
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="6" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="4" t="inlineStr"/>
-      <c r="B16" s="4" t="inlineStr"/>
-      <c r="C16" s="4" t="inlineStr"/>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="4" t="inlineStr"/>
-      <c r="I16" s="4" t="inlineStr"/>
-      <c r="J16" s="4" t="inlineStr"/>
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n"/>
+      <c r="J16" s="6" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="4" t="inlineStr"/>
-      <c r="B17" s="4" t="inlineStr"/>
-      <c r="C17" s="4" t="inlineStr"/>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="inlineStr"/>
-      <c r="I17" s="4" t="inlineStr"/>
-      <c r="J17" s="4" t="inlineStr"/>
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="6" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="4" t="inlineStr"/>
-      <c r="B18" s="4" t="inlineStr"/>
-      <c r="C18" s="4" t="inlineStr"/>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr"/>
-      <c r="I18" s="4" t="inlineStr"/>
-      <c r="J18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="4" t="inlineStr"/>
-      <c r="B19" s="4" t="inlineStr"/>
-      <c r="C19" s="4" t="inlineStr"/>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr"/>
-      <c r="I19" s="4" t="inlineStr"/>
-      <c r="J19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="4" t="inlineStr"/>
-      <c r="B20" s="4" t="inlineStr"/>
-      <c r="C20" s="4" t="inlineStr"/>
-      <c r="D20" s="4" t="inlineStr"/>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="4" t="inlineStr"/>
-      <c r="I20" s="4" t="inlineStr"/>
-      <c r="J20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="4" t="inlineStr"/>
-      <c r="B21" s="4" t="inlineStr"/>
-      <c r="C21" s="4" t="inlineStr"/>
-      <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="4" t="inlineStr"/>
-      <c r="J21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="4" t="inlineStr"/>
-      <c r="B22" s="4" t="inlineStr"/>
-      <c r="C22" s="4" t="inlineStr"/>
-      <c r="D22" s="4" t="inlineStr"/>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr"/>
-      <c r="H22" s="4" t="inlineStr"/>
-      <c r="I22" s="4" t="inlineStr"/>
-      <c r="J22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="4" t="inlineStr"/>
-      <c r="B23" s="4" t="inlineStr"/>
-      <c r="C23" s="4" t="inlineStr"/>
-      <c r="D23" s="4" t="inlineStr"/>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="4" t="inlineStr"/>
-      <c r="I23" s="4" t="inlineStr"/>
-      <c r="J23" s="4" t="inlineStr"/>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>【更新が必要な資格の例】サービス管理責任者現任研修：5年毎 / 相談支援専門員現任研修：5年毎 / 認定看護師：5年毎</t>
-        </is>
-      </c>
+      <c r="A18" s="6" t="n"/>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="6" t="n"/>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>※ 管理者・サービス管理責任者・児発管・看護職員・生活支援員等の配置と資格を最新に保つ。
+　 サビ管は5年ごとの更新研修、強度行動障害・喀痰吸引等の研修修了も記録。</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="8" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A25:J25"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>